--- a/output/pdf_financials_xlsx/HDRO.xlsx
+++ b/output/pdf_financials_xlsx/HDRO.xlsx
@@ -1283,22 +1283,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.320057</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.399993</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.192568</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.105072</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.052594</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.692194</v>
       </c>
     </row>
     <row r="35">
@@ -1333,22 +1333,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.320057</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.399993</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.192568</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.105072</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.052594</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.692194</v>
       </c>
     </row>
     <row r="37">
@@ -1633,19 +1633,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.320057</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.399993</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.195338</v>
+        <v>0.00277</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.106177</v>
+        <v>0.001105</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.167202</v>
+        <v>0.114608</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/HDRO.xlsx
+++ b/output/pdf_financials_xlsx/HDRO.xlsx
@@ -2971,13 +2971,13 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.014239</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.010659</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.008782999999999999</v>
       </c>
       <c r="F101" s="3" t="n">
         <v>0.00252</v>
@@ -3099,10 +3099,10 @@
         <v>-0.271006</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.001578</v>
+        <v>-0.012237</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.001127</v>
+        <v>0.007656</v>
       </c>
       <c r="F106" s="3" t="n">
         <v>0.045699</v>
@@ -6470,7 +6470,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -7276,7 +7280,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
